--- a/sources/table_normalization/xlsx/economy-table83.xlsx
+++ b/sources/table_normalization/xlsx/economy-table83.xlsx
@@ -788,12 +788,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor theme="4" tint="0.79995117038483843"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor theme="4"/>
       </patternFill>
     </fill>
@@ -806,6 +800,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor theme="4" tint="0.79995117038483843"/>
       </patternFill>
     </fill>
@@ -895,7 +895,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -947,36 +947,29 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -985,15 +978,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1014,264 +998,25 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Денежный" xfId="1" builtinId="4"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF9966FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF66FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF993366"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF6AD492"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39991454817346722"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF66FFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.39991454817346722"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39991454817346722"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFCCCC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF9966FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF66FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF993366"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF6AD492"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39991454817346722"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF66FFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.39991454817346722"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39991454817346722"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFCCCC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1465,25 +1210,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="52"/>
-      <tableStyleElement type="headerRow" dxfId="51"/>
-      <tableStyleElement type="totalRow" dxfId="50"/>
-      <tableStyleElement type="firstColumn" dxfId="49"/>
-      <tableStyleElement type="lastColumn" dxfId="48"/>
-      <tableStyleElement type="firstRowStripe" dxfId="47"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="46"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="45"/>
-      <tableStyleElement type="totalRow" dxfId="44"/>
-      <tableStyleElement type="firstRowStripe" dxfId="43"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="42"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="41"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="40"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="39"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="38"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="37"/>
-      <tableStyleElement type="pageFieldValues" dxfId="36"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1782,14 +1527,14 @@
       <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="28"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="7">
         <v>8931.9699999999993</v>
       </c>
@@ -1798,7 +1543,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="38">
+      <c r="A3" s="32">
         <v>42705</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1820,7 +1565,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="39"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
@@ -1840,7 +1585,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="39"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1860,7 +1605,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="39"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1880,7 +1625,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="39"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1903,7 +1648,7 @@
       <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="39"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -1923,7 +1668,7 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="40"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1943,7 +1688,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="35">
+      <c r="A10" s="29">
         <v>42706</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1967,7 +1712,7 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="36"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1987,7 +1732,7 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="36"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
@@ -2007,7 +1752,7 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="36"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2027,7 +1772,7 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="37"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="4" t="s">
         <v>26</v>
       </c>
@@ -2047,7 +1792,7 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="38">
+      <c r="A15" s="32">
         <v>42709</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2071,7 +1816,7 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="39"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
@@ -2091,7 +1836,7 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="39"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
@@ -2111,7 +1856,7 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="39"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="4" t="s">
         <v>10</v>
       </c>
@@ -2131,7 +1876,7 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="39"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="1" t="s">
         <v>10</v>
       </c>
@@ -2151,7 +1896,7 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="39"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="4" t="s">
         <v>10</v>
       </c>
@@ -2171,7 +1916,7 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="39"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
@@ -2191,7 +1936,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="39"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="4" t="s">
         <v>10</v>
       </c>
@@ -2211,7 +1956,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="39"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
@@ -2231,7 +1976,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="39"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="4" t="s">
         <v>26</v>
       </c>
@@ -2251,7 +1996,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="39"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
@@ -2271,7 +2016,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="39"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="4" t="s">
         <v>24</v>
       </c>
@@ -2291,14 +2036,14 @@
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="39"/>
-      <c r="B27" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="30" t="s">
+      <c r="A27" s="33"/>
+      <c r="B27" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="25">
         <v>600</v>
       </c>
       <c r="E27" s="9" t="s">
@@ -2313,14 +2058,14 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="39"/>
-      <c r="B28" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="33" t="s">
+      <c r="A28" s="33"/>
+      <c r="B28" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="28">
         <v>675</v>
       </c>
       <c r="E28" s="10" t="s">
@@ -2335,14 +2080,14 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="39"/>
-      <c r="B29" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="30" t="s">
+      <c r="A29" s="33"/>
+      <c r="B29" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="25">
         <v>600</v>
       </c>
       <c r="E29" s="9" t="s">
@@ -2357,14 +2102,14 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="39"/>
-      <c r="B30" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="33" t="s">
+      <c r="A30" s="33"/>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="28">
         <v>350</v>
       </c>
       <c r="E30" s="10" t="s">
@@ -2379,14 +2124,14 @@
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="39"/>
-      <c r="B31" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="30" t="s">
+      <c r="A31" s="33"/>
+      <c r="B31" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="25">
         <v>550</v>
       </c>
       <c r="E31" s="9" t="s">
@@ -2401,14 +2146,14 @@
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="39"/>
-      <c r="B32" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="33" t="s">
+      <c r="A32" s="33"/>
+      <c r="B32" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="28">
         <v>520</v>
       </c>
       <c r="E32" s="10" t="s">
@@ -2423,14 +2168,14 @@
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="39"/>
-      <c r="B33" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="30" t="s">
+      <c r="A33" s="33"/>
+      <c r="B33" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="25">
         <v>1191</v>
       </c>
       <c r="E33" s="9" t="s">
@@ -2445,7 +2190,7 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="40"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="4" t="s">
         <v>17</v>
       </c>
@@ -2465,7 +2210,7 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="38">
+      <c r="A35" s="32">
         <v>42710</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2489,7 +2234,7 @@
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="39"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="4" t="s">
         <v>10</v>
       </c>
@@ -2509,7 +2254,7 @@
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="39"/>
+      <c r="A37" s="33"/>
       <c r="B37" s="1" t="s">
         <v>10</v>
       </c>
@@ -2529,7 +2274,7 @@
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="39"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="4" t="s">
         <v>10</v>
       </c>
@@ -2549,7 +2294,7 @@
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="39"/>
+      <c r="A39" s="33"/>
       <c r="B39" s="1" t="s">
         <v>26</v>
       </c>
@@ -2569,7 +2314,7 @@
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="39"/>
+      <c r="A40" s="33"/>
       <c r="B40" s="4" t="s">
         <v>34</v>
       </c>
@@ -2589,7 +2334,7 @@
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="40"/>
+      <c r="A41" s="34"/>
       <c r="B41" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,7 +2354,7 @@
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="35">
+      <c r="A42" s="29">
         <v>42711</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -2633,7 +2378,7 @@
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="36"/>
+      <c r="A43" s="30"/>
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
@@ -2653,7 +2398,7 @@
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="36"/>
+      <c r="A44" s="30"/>
       <c r="B44" s="4" t="s">
         <v>34</v>
       </c>
@@ -2673,7 +2418,7 @@
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="37"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="1" t="s">
         <v>10</v>
       </c>
@@ -2693,7 +2438,7 @@
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="35">
+      <c r="A46" s="29">
         <v>42712</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -2717,7 +2462,7 @@
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="36"/>
+      <c r="A47" s="30"/>
       <c r="B47" s="1" t="s">
         <v>24</v>
       </c>
@@ -2737,7 +2482,7 @@
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="36"/>
+      <c r="A48" s="30"/>
       <c r="B48" s="4" t="s">
         <v>24</v>
       </c>
@@ -2757,7 +2502,7 @@
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="36"/>
+      <c r="A49" s="30"/>
       <c r="B49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2777,7 +2522,7 @@
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="36"/>
+      <c r="A50" s="30"/>
       <c r="B50" s="4" t="s">
         <v>10</v>
       </c>
@@ -2797,7 +2542,7 @@
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="36"/>
+      <c r="A51" s="30"/>
       <c r="B51" s="1" t="s">
         <v>10</v>
       </c>
@@ -2817,7 +2562,7 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="37"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="4" t="s">
         <v>26</v>
       </c>
@@ -2837,7 +2582,7 @@
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="38">
+      <c r="A53" s="32">
         <v>42713</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -2861,7 +2606,7 @@
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="39"/>
+      <c r="A54" s="33"/>
       <c r="B54" s="4" t="s">
         <v>20</v>
       </c>
@@ -2883,7 +2628,7 @@
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="39"/>
+      <c r="A55" s="33"/>
       <c r="B55" s="1" t="s">
         <v>10</v>
       </c>
@@ -2903,7 +2648,7 @@
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="39"/>
+      <c r="A56" s="33"/>
       <c r="B56" s="4" t="s">
         <v>10</v>
       </c>
@@ -2923,7 +2668,7 @@
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="39"/>
+      <c r="A57" s="33"/>
       <c r="B57" s="1" t="s">
         <v>15</v>
       </c>
@@ -2943,7 +2688,7 @@
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="40"/>
+      <c r="A58" s="34"/>
       <c r="B58" s="4" t="s">
         <v>15</v>
       </c>
@@ -2965,7 +2710,7 @@
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="38">
+      <c r="A59" s="32">
         <v>42716</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -2989,7 +2734,7 @@
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="39"/>
+      <c r="A60" s="33"/>
       <c r="B60" s="4" t="s">
         <v>20</v>
       </c>
@@ -3011,7 +2756,7 @@
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="39"/>
+      <c r="A61" s="33"/>
       <c r="B61" s="1" t="s">
         <v>10</v>
       </c>
@@ -3031,7 +2776,7 @@
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="39"/>
+      <c r="A62" s="33"/>
       <c r="B62" s="4" t="s">
         <v>10</v>
       </c>
@@ -3051,7 +2796,7 @@
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="39"/>
+      <c r="A63" s="33"/>
       <c r="B63" s="1" t="s">
         <v>10</v>
       </c>
@@ -3071,7 +2816,7 @@
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="39"/>
+      <c r="A64" s="33"/>
       <c r="B64" s="4" t="s">
         <v>10</v>
       </c>
@@ -3091,7 +2836,7 @@
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="39"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="1" t="s">
         <v>10</v>
       </c>
@@ -3111,7 +2856,7 @@
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="39"/>
+      <c r="A66" s="33"/>
       <c r="B66" s="4" t="s">
         <v>34</v>
       </c>
@@ -3131,7 +2876,7 @@
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="39"/>
+      <c r="A67" s="33"/>
       <c r="B67" s="1" t="s">
         <v>10</v>
       </c>
@@ -3151,7 +2896,7 @@
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="39"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="4" t="s">
         <v>10</v>
       </c>
@@ -3171,7 +2916,7 @@
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="39"/>
+      <c r="A69" s="33"/>
       <c r="B69" s="1" t="s">
         <v>10</v>
       </c>
@@ -3191,7 +2936,7 @@
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="39"/>
+      <c r="A70" s="33"/>
       <c r="B70" s="1" t="s">
         <v>15</v>
       </c>
@@ -3213,7 +2958,7 @@
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="39"/>
+      <c r="A71" s="33"/>
       <c r="B71" s="1" t="s">
         <v>15</v>
       </c>
@@ -3235,7 +2980,7 @@
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="39"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="1" t="s">
         <v>15</v>
       </c>
@@ -3257,7 +3002,7 @@
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="39"/>
+      <c r="A73" s="33"/>
       <c r="B73" s="1" t="s">
         <v>15</v>
       </c>
@@ -3279,7 +3024,7 @@
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="39"/>
+      <c r="A74" s="33"/>
       <c r="B74" s="4" t="s">
         <v>17</v>
       </c>
@@ -3299,7 +3044,7 @@
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="40"/>
+      <c r="A75" s="34"/>
       <c r="B75" s="1" t="s">
         <v>17</v>
       </c>
@@ -3319,7 +3064,7 @@
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="35">
+      <c r="A76" s="29">
         <v>42717</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -3341,7 +3086,7 @@
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="36"/>
+      <c r="A77" s="30"/>
       <c r="B77" s="1" t="s">
         <v>10</v>
       </c>
@@ -3361,7 +3106,7 @@
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="36"/>
+      <c r="A78" s="30"/>
       <c r="B78" s="4" t="s">
         <v>24</v>
       </c>
@@ -3381,7 +3126,7 @@
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="36"/>
+      <c r="A79" s="30"/>
       <c r="B79" s="1" t="s">
         <v>34</v>
       </c>
@@ -3401,7 +3146,7 @@
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="36"/>
+      <c r="A80" s="30"/>
       <c r="B80" s="4" t="s">
         <v>26</v>
       </c>
@@ -3421,7 +3166,7 @@
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="36"/>
+      <c r="A81" s="30"/>
       <c r="B81" s="1" t="s">
         <v>15</v>
       </c>
@@ -3443,7 +3188,7 @@
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="36"/>
+      <c r="A82" s="30"/>
       <c r="B82" s="4" t="s">
         <v>15</v>
       </c>
@@ -3465,7 +3210,7 @@
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="36"/>
+      <c r="A83" s="30"/>
       <c r="B83" s="1" t="s">
         <v>15</v>
       </c>
@@ -3487,7 +3232,7 @@
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="36"/>
+      <c r="A84" s="30"/>
       <c r="B84" s="4" t="s">
         <v>17</v>
       </c>
@@ -3507,7 +3252,7 @@
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="37"/>
+      <c r="A85" s="31"/>
       <c r="B85" s="1" t="s">
         <v>17</v>
       </c>
@@ -3527,7 +3272,7 @@
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="35">
+      <c r="A86" s="29">
         <v>42718</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -3551,7 +3296,7 @@
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="36"/>
+      <c r="A87" s="30"/>
       <c r="B87" s="1" t="s">
         <v>96</v>
       </c>
@@ -3571,7 +3316,7 @@
       </c>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="37"/>
+      <c r="A88" s="31"/>
       <c r="B88" s="4" t="s">
         <v>20</v>
       </c>
@@ -3591,7 +3336,7 @@
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="38">
+      <c r="A89" s="32">
         <v>42719</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -3615,7 +3360,7 @@
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="39"/>
+      <c r="A90" s="33"/>
       <c r="B90" s="4" t="s">
         <v>10</v>
       </c>
@@ -3635,7 +3380,7 @@
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="39"/>
+      <c r="A91" s="33"/>
       <c r="B91" s="1" t="s">
         <v>24</v>
       </c>
@@ -3655,7 +3400,7 @@
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="40"/>
+      <c r="A92" s="34"/>
       <c r="B92" s="4" t="s">
         <v>10</v>
       </c>
@@ -3675,7 +3420,7 @@
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="38">
+      <c r="A93" s="32">
         <v>42720</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -3699,7 +3444,7 @@
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="39"/>
+      <c r="A94" s="33"/>
       <c r="B94" s="4" t="s">
         <v>20</v>
       </c>
@@ -3721,7 +3466,7 @@
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="39"/>
+      <c r="A95" s="33"/>
       <c r="B95" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,7 +3488,7 @@
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="39"/>
+      <c r="A96" s="33"/>
       <c r="B96" s="4" t="s">
         <v>26</v>
       </c>
@@ -3763,7 +3508,7 @@
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="39"/>
+      <c r="A97" s="33"/>
       <c r="B97" s="1" t="s">
         <v>10</v>
       </c>
@@ -3783,7 +3528,7 @@
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="39"/>
+      <c r="A98" s="33"/>
       <c r="B98" s="4" t="s">
         <v>10</v>
       </c>
@@ -3803,7 +3548,7 @@
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="39"/>
+      <c r="A99" s="33"/>
       <c r="B99" s="1" t="s">
         <v>10</v>
       </c>
@@ -3823,7 +3568,7 @@
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="40"/>
+      <c r="A100" s="34"/>
       <c r="B100" s="4" t="s">
         <v>34</v>
       </c>
@@ -3843,7 +3588,7 @@
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="38">
+      <c r="A101" s="32">
         <v>42723</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -3867,7 +3612,7 @@
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="39"/>
+      <c r="A102" s="33"/>
       <c r="B102" s="4" t="s">
         <v>10</v>
       </c>
@@ -3887,7 +3632,7 @@
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="39"/>
+      <c r="A103" s="33"/>
       <c r="B103" s="1" t="s">
         <v>10</v>
       </c>
@@ -3907,7 +3652,7 @@
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="39"/>
+      <c r="A104" s="33"/>
       <c r="B104" s="4" t="s">
         <v>34</v>
       </c>
@@ -3927,7 +3672,7 @@
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="39"/>
+      <c r="A105" s="33"/>
       <c r="B105" s="1" t="s">
         <v>10</v>
       </c>
@@ -3947,7 +3692,7 @@
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="39"/>
+      <c r="A106" s="33"/>
       <c r="B106" s="4" t="s">
         <v>10</v>
       </c>
@@ -3967,7 +3712,7 @@
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="39"/>
+      <c r="A107" s="33"/>
       <c r="B107" s="1" t="s">
         <v>10</v>
       </c>
@@ -3987,7 +3732,7 @@
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="39"/>
+      <c r="A108" s="33"/>
       <c r="B108" s="4" t="s">
         <v>34</v>
       </c>
@@ -4007,7 +3752,7 @@
       </c>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="39"/>
+      <c r="A109" s="33"/>
       <c r="B109" s="1" t="s">
         <v>26</v>
       </c>
@@ -4027,7 +3772,7 @@
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="39"/>
+      <c r="A110" s="33"/>
       <c r="B110" s="4" t="s">
         <v>10</v>
       </c>
@@ -4047,7 +3792,7 @@
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="39"/>
+      <c r="A111" s="33"/>
       <c r="B111" s="1" t="s">
         <v>24</v>
       </c>
@@ -4067,7 +3812,7 @@
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="39"/>
+      <c r="A112" s="33"/>
       <c r="B112" s="4" t="s">
         <v>10</v>
       </c>
@@ -4087,7 +3832,7 @@
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="39"/>
+      <c r="A113" s="33"/>
       <c r="B113" s="1" t="s">
         <v>10</v>
       </c>
@@ -4107,7 +3852,7 @@
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="39"/>
+      <c r="A114" s="33"/>
       <c r="B114" s="4" t="s">
         <v>96</v>
       </c>
@@ -4127,7 +3872,7 @@
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="39"/>
+      <c r="A115" s="33"/>
       <c r="B115" s="1" t="s">
         <v>125</v>
       </c>
@@ -4145,7 +3890,7 @@
       <c r="H115" s="17"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="39"/>
+      <c r="A116" s="33"/>
       <c r="B116" s="4" t="s">
         <v>10</v>
       </c>
@@ -4163,7 +3908,7 @@
       <c r="H116" s="17"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="39"/>
+      <c r="A117" s="33"/>
       <c r="B117" s="1" t="s">
         <v>10</v>
       </c>
@@ -4181,7 +3926,7 @@
       <c r="H117" s="17"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="39"/>
+      <c r="A118" s="33"/>
       <c r="B118" s="4" t="s">
         <v>10</v>
       </c>
@@ -4199,7 +3944,7 @@
       <c r="H118" s="17"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="39"/>
+      <c r="A119" s="33"/>
       <c r="B119" s="1" t="s">
         <v>15</v>
       </c>
@@ -4219,7 +3964,7 @@
       <c r="H119" s="17"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="39"/>
+      <c r="A120" s="33"/>
       <c r="B120" s="4" t="s">
         <v>15</v>
       </c>
@@ -4239,7 +3984,7 @@
       <c r="H120" s="17"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="39"/>
+      <c r="A121" s="33"/>
       <c r="B121" s="1" t="s">
         <v>15</v>
       </c>
@@ -4259,7 +4004,7 @@
       <c r="H121" s="17"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="39"/>
+      <c r="A122" s="33"/>
       <c r="B122" s="4" t="s">
         <v>15</v>
       </c>
@@ -4279,7 +4024,7 @@
       <c r="H122" s="17"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="39"/>
+      <c r="A123" s="33"/>
       <c r="B123" s="1" t="s">
         <v>17</v>
       </c>
@@ -4297,7 +4042,7 @@
       <c r="H123" s="17"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="40"/>
+      <c r="A124" s="34"/>
       <c r="B124" s="4" t="s">
         <v>17</v>
       </c>
@@ -4315,7 +4060,7 @@
       <c r="H124" s="17"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="38">
+      <c r="A125" s="32">
         <v>42724</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -4337,7 +4082,7 @@
       <c r="H125" s="17"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="39"/>
+      <c r="A126" s="33"/>
       <c r="B126" s="4" t="s">
         <v>20</v>
       </c>
@@ -4357,7 +4102,7 @@
       <c r="H126" s="17"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="39"/>
+      <c r="A127" s="33"/>
       <c r="B127" s="1" t="s">
         <v>10</v>
       </c>
@@ -4375,7 +4120,7 @@
       <c r="H127" s="17"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="39"/>
+      <c r="A128" s="33"/>
       <c r="B128" s="4" t="s">
         <v>10</v>
       </c>
@@ -4393,7 +4138,7 @@
       <c r="H128" s="17"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="39"/>
+      <c r="A129" s="33"/>
       <c r="B129" s="1" t="s">
         <v>10</v>
       </c>
@@ -4411,7 +4156,7 @@
       <c r="H129" s="17"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="40"/>
+      <c r="A130" s="34"/>
       <c r="B130" s="4" t="s">
         <v>15</v>
       </c>
@@ -4429,7 +4174,7 @@
       <c r="H130" s="17"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="38">
+      <c r="A131" s="32">
         <v>42725</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -4449,7 +4194,7 @@
       <c r="H131" s="17"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="39"/>
+      <c r="A132" s="33"/>
       <c r="B132" s="4" t="s">
         <v>96</v>
       </c>
@@ -4467,7 +4212,7 @@
       <c r="H132" s="17"/>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="39"/>
+      <c r="A133" s="33"/>
       <c r="B133" s="1" t="s">
         <v>142</v>
       </c>
@@ -4485,7 +4230,7 @@
       <c r="H133" s="17"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="39"/>
+      <c r="A134" s="33"/>
       <c r="B134" s="4" t="s">
         <v>15</v>
       </c>
@@ -4505,7 +4250,7 @@
       <c r="H134" s="17"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="39"/>
+      <c r="A135" s="33"/>
       <c r="B135" s="1" t="s">
         <v>15</v>
       </c>
@@ -4525,7 +4270,7 @@
       <c r="H135" s="17"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="39"/>
+      <c r="A136" s="33"/>
       <c r="B136" s="4" t="s">
         <v>17</v>
       </c>
@@ -4543,7 +4288,7 @@
       <c r="H136" s="17"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="40"/>
+      <c r="A137" s="34"/>
       <c r="B137" s="1" t="s">
         <v>17</v>
       </c>
@@ -4561,7 +4306,7 @@
       <c r="H137" s="17"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="35">
+      <c r="A138" s="29">
         <v>42726</v>
       </c>
       <c r="B138" s="4" t="s">
@@ -4581,7 +4326,7 @@
       <c r="H138" s="17"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="36"/>
+      <c r="A139" s="30"/>
       <c r="B139" s="1" t="s">
         <v>10</v>
       </c>
@@ -4599,7 +4344,7 @@
       <c r="H139" s="17"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="36"/>
+      <c r="A140" s="30"/>
       <c r="B140" s="4" t="s">
         <v>26</v>
       </c>
@@ -4617,7 +4362,7 @@
       <c r="H140" s="17"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="36"/>
+      <c r="A141" s="30"/>
       <c r="B141" s="1" t="s">
         <v>10</v>
       </c>
@@ -4635,7 +4380,7 @@
       <c r="H141" s="17"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="36"/>
+      <c r="A142" s="30"/>
       <c r="B142" s="4" t="s">
         <v>15</v>
       </c>
@@ -4653,7 +4398,7 @@
       <c r="H142" s="17"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="36"/>
+      <c r="A143" s="30"/>
       <c r="B143" s="1" t="s">
         <v>10</v>
       </c>
@@ -4671,7 +4416,7 @@
       <c r="H143" s="17"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="36"/>
+      <c r="A144" s="30"/>
       <c r="B144" s="4" t="s">
         <v>142</v>
       </c>
@@ -4689,7 +4434,7 @@
       <c r="H144" s="17"/>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="36"/>
+      <c r="A145" s="30"/>
       <c r="B145" s="1" t="s">
         <v>15</v>
       </c>
@@ -4707,7 +4452,7 @@
       <c r="H145" s="17"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="36"/>
+      <c r="A146" s="30"/>
       <c r="B146" s="4" t="s">
         <v>15</v>
       </c>
@@ -4725,7 +4470,7 @@
       <c r="H146" s="17"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="37"/>
+      <c r="A147" s="31"/>
       <c r="B147" s="1" t="s">
         <v>10</v>
       </c>
@@ -4743,7 +4488,7 @@
       <c r="H147" s="17"/>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="35">
+      <c r="A148" s="29">
         <v>42727</v>
       </c>
       <c r="B148" s="4" t="s">
@@ -4763,7 +4508,7 @@
       <c r="H148" s="17"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="36"/>
+      <c r="A149" s="30"/>
       <c r="B149" s="1" t="s">
         <v>20</v>
       </c>
@@ -4781,7 +4526,7 @@
       <c r="H149" s="17"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="36"/>
+      <c r="A150" s="30"/>
       <c r="B150" s="4" t="s">
         <v>10</v>
       </c>
@@ -4799,7 +4544,7 @@
       <c r="H150" s="17"/>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="36"/>
+      <c r="A151" s="30"/>
       <c r="B151" s="1" t="s">
         <v>10</v>
       </c>
@@ -4817,7 +4562,7 @@
       <c r="H151" s="17"/>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="36"/>
+      <c r="A152" s="30"/>
       <c r="B152" s="4" t="s">
         <v>10</v>
       </c>
@@ -4835,7 +4580,7 @@
       <c r="H152" s="17"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="36"/>
+      <c r="A153" s="30"/>
       <c r="B153" s="1" t="s">
         <v>34</v>
       </c>
@@ -4853,7 +4598,7 @@
       <c r="H153" s="17"/>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="36"/>
+      <c r="A154" s="30"/>
       <c r="B154" s="4" t="s">
         <v>15</v>
       </c>
@@ -4873,7 +4618,7 @@
       <c r="H154" s="17"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="36"/>
+      <c r="A155" s="30"/>
       <c r="B155" s="1" t="s">
         <v>15</v>
       </c>
@@ -4893,7 +4638,7 @@
       <c r="H155" s="17"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="36"/>
+      <c r="A156" s="30"/>
       <c r="B156" s="4" t="s">
         <v>15</v>
       </c>
@@ -4913,7 +4658,7 @@
       <c r="H156" s="17"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="36"/>
+      <c r="A157" s="30"/>
       <c r="B157" s="1" t="s">
         <v>15</v>
       </c>
@@ -4933,7 +4678,7 @@
       <c r="H157" s="17"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="37"/>
+      <c r="A158" s="31"/>
       <c r="B158" s="4" t="s">
         <v>15</v>
       </c>
@@ -4953,7 +4698,7 @@
       <c r="H158" s="17"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="38">
+      <c r="A159" s="32">
         <v>42731</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -4975,7 +4720,7 @@
       <c r="H159" s="17"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="39"/>
+      <c r="A160" s="33"/>
       <c r="B160" s="4" t="s">
         <v>34</v>
       </c>
@@ -4993,7 +4738,7 @@
       <c r="H160" s="17"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="39"/>
+      <c r="A161" s="33"/>
       <c r="B161" s="1" t="s">
         <v>10</v>
       </c>
@@ -5011,7 +4756,7 @@
       <c r="H161" s="17"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="39"/>
+      <c r="A162" s="33"/>
       <c r="B162" s="4" t="s">
         <v>10</v>
       </c>
@@ -5029,7 +4774,7 @@
       <c r="H162" s="17"/>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="39"/>
+      <c r="A163" s="33"/>
       <c r="B163" s="1" t="s">
         <v>10</v>
       </c>
@@ -5047,7 +4792,7 @@
       <c r="H163" s="17"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="39"/>
+      <c r="A164" s="33"/>
       <c r="B164" s="4" t="s">
         <v>26</v>
       </c>
@@ -5065,7 +4810,7 @@
       <c r="H164" s="17"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="39"/>
+      <c r="A165" s="33"/>
       <c r="B165" s="1" t="s">
         <v>10</v>
       </c>
@@ -5083,7 +4828,7 @@
       <c r="H165" s="17"/>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="39"/>
+      <c r="A166" s="33"/>
       <c r="B166" s="4" t="s">
         <v>24</v>
       </c>
@@ -5101,7 +4846,7 @@
       <c r="H166" s="17"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="39"/>
+      <c r="A167" s="33"/>
       <c r="B167" s="1" t="s">
         <v>10</v>
       </c>
@@ -5119,7 +4864,7 @@
       <c r="H167" s="17"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="39"/>
+      <c r="A168" s="33"/>
       <c r="B168" s="4" t="s">
         <v>15</v>
       </c>
@@ -5137,7 +4882,7 @@
       <c r="H168" s="17"/>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="39"/>
+      <c r="A169" s="33"/>
       <c r="B169" s="1" t="s">
         <v>10</v>
       </c>
@@ -5155,7 +4900,7 @@
       <c r="H169" s="17"/>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="39"/>
+      <c r="A170" s="33"/>
       <c r="B170" s="4" t="s">
         <v>142</v>
       </c>
@@ -5173,7 +4918,7 @@
       <c r="H170" s="17"/>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="39"/>
+      <c r="A171" s="33"/>
       <c r="B171" s="1" t="s">
         <v>15</v>
       </c>
@@ -5191,7 +4936,7 @@
       <c r="H171" s="17"/>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="39"/>
+      <c r="A172" s="33"/>
       <c r="B172" s="4" t="s">
         <v>10</v>
       </c>
@@ -5209,7 +4954,7 @@
       <c r="H172" s="17"/>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="39"/>
+      <c r="A173" s="33"/>
       <c r="B173" s="1" t="s">
         <v>10</v>
       </c>
@@ -5227,7 +4972,7 @@
       <c r="H173" s="17"/>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="39"/>
+      <c r="A174" s="33"/>
       <c r="B174" s="4" t="s">
         <v>34</v>
       </c>
@@ -5245,7 +4990,7 @@
       <c r="H174" s="17"/>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="39"/>
+      <c r="A175" s="33"/>
       <c r="B175" s="1" t="s">
         <v>15</v>
       </c>
@@ -5265,7 +5010,7 @@
       <c r="H175" s="17"/>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="39"/>
+      <c r="A176" s="33"/>
       <c r="B176" s="4" t="s">
         <v>15</v>
       </c>
@@ -5285,7 +5030,7 @@
       <c r="H176" s="17"/>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="39"/>
+      <c r="A177" s="33"/>
       <c r="B177" s="1" t="s">
         <v>15</v>
       </c>
@@ -5305,7 +5050,7 @@
       <c r="H177" s="17"/>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="39"/>
+      <c r="A178" s="33"/>
       <c r="B178" s="4" t="s">
         <v>15</v>
       </c>
@@ -5325,7 +5070,7 @@
       <c r="H178" s="17"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="39"/>
+      <c r="A179" s="33"/>
       <c r="B179" s="1" t="s">
         <v>15</v>
       </c>
@@ -5345,7 +5090,7 @@
       <c r="H179" s="17"/>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="39"/>
+      <c r="A180" s="33"/>
       <c r="B180" s="4" t="s">
         <v>15</v>
       </c>
@@ -5365,7 +5110,7 @@
       <c r="H180" s="17"/>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="39"/>
+      <c r="A181" s="33"/>
       <c r="B181" s="1" t="s">
         <v>15</v>
       </c>
@@ -5385,7 +5130,7 @@
       <c r="H181" s="17"/>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="39"/>
+      <c r="A182" s="33"/>
       <c r="B182" s="4" t="s">
         <v>15</v>
       </c>
@@ -5405,7 +5150,7 @@
       <c r="H182" s="17"/>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="39"/>
+      <c r="A183" s="33"/>
       <c r="B183" s="1" t="s">
         <v>15</v>
       </c>
@@ -5425,7 +5170,7 @@
       <c r="H183" s="17"/>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="39"/>
+      <c r="A184" s="33"/>
       <c r="B184" s="4" t="s">
         <v>15</v>
       </c>
@@ -5445,7 +5190,7 @@
       <c r="H184" s="17"/>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="39"/>
+      <c r="A185" s="33"/>
       <c r="B185" s="1" t="s">
         <v>17</v>
       </c>
@@ -5463,7 +5208,7 @@
       <c r="H185" s="17"/>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="39"/>
+      <c r="A186" s="33"/>
       <c r="B186" s="4" t="s">
         <v>17</v>
       </c>
@@ -5481,7 +5226,7 @@
       <c r="H186" s="17"/>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="39"/>
+      <c r="A187" s="33"/>
       <c r="B187" s="1" t="s">
         <v>17</v>
       </c>
@@ -5499,7 +5244,7 @@
       <c r="H187" s="17"/>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="39"/>
+      <c r="A188" s="33"/>
       <c r="B188" s="4" t="s">
         <v>17</v>
       </c>
@@ -5517,7 +5262,7 @@
       <c r="H188" s="17"/>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="40"/>
+      <c r="A189" s="34"/>
       <c r="B189" s="1" t="s">
         <v>17</v>
       </c>
@@ -5535,7 +5280,7 @@
       <c r="H189" s="17"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="35">
+      <c r="A190" s="29">
         <v>42732</v>
       </c>
       <c r="B190" s="4" t="s">
@@ -5557,7 +5302,7 @@
       <c r="H190" s="17"/>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="36"/>
+      <c r="A191" s="30"/>
       <c r="B191" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,7 +5322,7 @@
       <c r="H191" s="17"/>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="36"/>
+      <c r="A192" s="30"/>
       <c r="B192" s="4" t="s">
         <v>20</v>
       </c>
@@ -5597,7 +5342,7 @@
       <c r="H192" s="17"/>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" s="36"/>
+      <c r="A193" s="30"/>
       <c r="B193" s="1" t="s">
         <v>20</v>
       </c>
@@ -5617,7 +5362,7 @@
       <c r="H193" s="17"/>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="36"/>
+      <c r="A194" s="30"/>
       <c r="B194" s="4" t="s">
         <v>10</v>
       </c>
@@ -5635,7 +5380,7 @@
       <c r="H194" s="17"/>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="36"/>
+      <c r="A195" s="30"/>
       <c r="B195" s="1" t="s">
         <v>10</v>
       </c>
@@ -5653,7 +5398,7 @@
       <c r="H195" s="17"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="36"/>
+      <c r="A196" s="30"/>
       <c r="B196" s="4" t="s">
         <v>24</v>
       </c>
@@ -5671,7 +5416,7 @@
       <c r="H196" s="17"/>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="36"/>
+      <c r="A197" s="30"/>
       <c r="B197" s="1" t="s">
         <v>10</v>
       </c>
@@ -5689,7 +5434,7 @@
       <c r="H197" s="17"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="36"/>
+      <c r="A198" s="30"/>
       <c r="B198" s="4" t="s">
         <v>24</v>
       </c>
@@ -5707,7 +5452,7 @@
       <c r="H198" s="17"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="36"/>
+      <c r="A199" s="30"/>
       <c r="B199" s="1" t="s">
         <v>34</v>
       </c>
@@ -5725,7 +5470,7 @@
       <c r="H199" s="17"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="36"/>
+      <c r="A200" s="30"/>
       <c r="B200" s="4" t="s">
         <v>15</v>
       </c>
@@ -5743,7 +5488,7 @@
       <c r="H200" s="17"/>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="37"/>
+      <c r="A201" s="31"/>
       <c r="B201" s="1" t="s">
         <v>15</v>
       </c>
@@ -5761,7 +5506,7 @@
       <c r="H201" s="17"/>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" s="35">
+      <c r="A202" s="29">
         <v>42733</v>
       </c>
       <c r="B202" s="4" t="s">
@@ -5781,7 +5526,7 @@
       <c r="H202" s="17"/>
     </row>
     <row r="203" spans="1:8">
-      <c r="A203" s="36"/>
+      <c r="A203" s="30"/>
       <c r="B203" s="1" t="s">
         <v>10</v>
       </c>
@@ -5799,7 +5544,7 @@
       <c r="H203" s="17"/>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="36"/>
+      <c r="A204" s="30"/>
       <c r="B204" s="4" t="s">
         <v>10</v>
       </c>
@@ -5817,7 +5562,7 @@
       <c r="H204" s="17"/>
     </row>
     <row r="205" spans="1:8">
-      <c r="A205" s="36"/>
+      <c r="A205" s="30"/>
       <c r="B205" s="1" t="s">
         <v>10</v>
       </c>
@@ -5835,7 +5580,7 @@
       <c r="H205" s="17"/>
     </row>
     <row r="206" spans="1:8">
-      <c r="A206" s="36"/>
+      <c r="A206" s="30"/>
       <c r="B206" s="4" t="s">
         <v>26</v>
       </c>
@@ -5853,7 +5598,7 @@
       <c r="H206" s="17"/>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="36"/>
+      <c r="A207" s="30"/>
       <c r="B207" s="1" t="s">
         <v>15</v>
       </c>
@@ -5873,7 +5618,7 @@
       <c r="H207" s="17"/>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" s="36"/>
+      <c r="A208" s="30"/>
       <c r="B208" s="4" t="s">
         <v>15</v>
       </c>
@@ -5893,7 +5638,7 @@
       <c r="H208" s="17"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="36"/>
+      <c r="A209" s="30"/>
       <c r="B209" s="1" t="s">
         <v>15</v>
       </c>
@@ -5913,7 +5658,7 @@
       <c r="H209" s="17"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="36"/>
+      <c r="A210" s="30"/>
       <c r="B210" s="4" t="s">
         <v>26</v>
       </c>
@@ -5931,7 +5676,7 @@
       <c r="H210" s="17"/>
     </row>
     <row r="211" spans="1:8">
-      <c r="A211" s="37"/>
+      <c r="A211" s="31"/>
       <c r="B211" s="1" t="s">
         <v>17</v>
       </c>
@@ -5949,7 +5694,7 @@
       <c r="H211" s="17"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="35">
+      <c r="A212" s="29">
         <v>42734</v>
       </c>
       <c r="B212" s="4" t="s">
@@ -5971,7 +5716,7 @@
       <c r="H212" s="17"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="36"/>
+      <c r="A213" s="30"/>
       <c r="B213" s="1" t="s">
         <v>20</v>
       </c>
@@ -5991,7 +5736,7 @@
       <c r="H213" s="17"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="36"/>
+      <c r="A214" s="30"/>
       <c r="B214" s="4" t="s">
         <v>10</v>
       </c>
@@ -6009,7 +5754,7 @@
       <c r="H214" s="17"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="36"/>
+      <c r="A215" s="30"/>
       <c r="B215" s="1" t="s">
         <v>10</v>
       </c>
@@ -6027,7 +5772,7 @@
       <c r="H215" s="17"/>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="36"/>
+      <c r="A216" s="30"/>
       <c r="B216" s="4" t="s">
         <v>96</v>
       </c>
@@ -6045,7 +5790,7 @@
       <c r="H216" s="17"/>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="36"/>
+      <c r="A217" s="30"/>
       <c r="B217" s="1" t="s">
         <v>96</v>
       </c>
@@ -6063,7 +5808,7 @@
       <c r="H217" s="17"/>
     </row>
     <row r="218" spans="1:8">
-      <c r="A218" s="36"/>
+      <c r="A218" s="30"/>
       <c r="B218" s="4" t="s">
         <v>10</v>
       </c>
@@ -6081,7 +5826,7 @@
       <c r="H218" s="17"/>
     </row>
     <row r="219" spans="1:8">
-      <c r="A219" s="36"/>
+      <c r="A219" s="30"/>
       <c r="B219" s="1" t="s">
         <v>26</v>
       </c>
@@ -6099,7 +5844,7 @@
       <c r="H219" s="17"/>
     </row>
     <row r="220" spans="1:8">
-      <c r="A220" s="36"/>
+      <c r="A220" s="30"/>
       <c r="B220" s="4" t="s">
         <v>15</v>
       </c>
@@ -6119,7 +5864,7 @@
       <c r="H220" s="17"/>
     </row>
     <row r="221" spans="1:8">
-      <c r="A221" s="37"/>
+      <c r="A221" s="31"/>
       <c r="B221" s="1" t="s">
         <v>15</v>
       </c>
